--- a/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Output_costs_by_tretspef-Users_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Output_costs_by_tretspef-Users_Raw.xlsx
@@ -923,19 +923,19 @@
         </is>
       </c>
       <c r="B23">
-        <v>36423.08</v>
+        <v>36419.56</v>
       </c>
       <c r="C23">
-        <v>12141</v>
+        <v>12140</v>
       </c>
       <c r="D23">
-        <v>10261.78</v>
+        <v>10260.37</v>
       </c>
       <c r="E23">
         <v>642.21</v>
       </c>
       <c r="F23">
-        <v>20367.76</v>
+        <v>20364.24</v>
       </c>
       <c r="G23">
         <v>3</v>
@@ -1542,19 +1542,19 @@
         </is>
       </c>
       <c r="B48">
-        <v>201580.55</v>
+        <v>200246.1</v>
       </c>
       <c r="C48">
-        <v>1482</v>
+        <v>1472</v>
       </c>
       <c r="D48">
-        <v>2460.71</v>
+        <v>2455.77</v>
       </c>
       <c r="E48">
-        <v>36.77</v>
+        <v>14.17</v>
       </c>
       <c r="F48">
-        <v>14705</v>
+        <v>14687.27</v>
       </c>
       <c r="G48">
         <v>136</v>
@@ -1964,16 +1964,16 @@
         </is>
       </c>
       <c r="B65">
-        <v>828.33</v>
+        <v>828.66</v>
       </c>
       <c r="C65">
         <v>276</v>
       </c>
       <c r="D65">
-        <v>97.66</v>
+        <v>97.47</v>
       </c>
       <c r="E65">
-        <v>163.34</v>
+        <v>163.67</v>
       </c>
       <c r="F65">
         <v>332.49</v>
@@ -2614,19 +2614,19 @@
         </is>
       </c>
       <c r="B91">
-        <v>2356.74</v>
+        <v>785.58</v>
       </c>
       <c r="C91">
-        <v>107</v>
+        <v>36</v>
       </c>
       <c r="D91">
-        <v>137.98</v>
+        <v>45.99</v>
       </c>
       <c r="E91">
-        <v>38.64</v>
+        <v>12.88</v>
       </c>
       <c r="F91">
-        <v>618.16</v>
+        <v>206.05</v>
       </c>
       <c r="G91">
         <v>41</v>

--- a/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Output_costs_by_tretspef-Users_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Output_costs_by_tretspef-Users_Raw.xlsx
@@ -398,19 +398,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>362850.66</v>
+        <v>349011.9</v>
       </c>
       <c r="C2">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="D2">
-        <v>328.87</v>
+        <v>313.84</v>
       </c>
       <c r="E2">
-        <v>137.91</v>
+        <v>135.31</v>
       </c>
       <c r="F2">
-        <v>5006.92</v>
+        <v>4777.91</v>
       </c>
       <c r="G2">
         <v>1062</v>
@@ -423,19 +423,19 @@
         </is>
       </c>
       <c r="B3">
-        <v>395104.92</v>
+        <v>400851.58</v>
       </c>
       <c r="C3">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="D3">
-        <v>381.98</v>
+        <v>384.37</v>
       </c>
       <c r="E3">
-        <v>117.98</v>
+        <v>118.14</v>
       </c>
       <c r="F3">
-        <v>5867.06</v>
+        <v>5855.61</v>
       </c>
       <c r="G3">
         <v>1043</v>
@@ -448,19 +448,19 @@
         </is>
       </c>
       <c r="B4">
-        <v>13052.5</v>
+        <v>12523.94</v>
       </c>
       <c r="C4">
-        <v>1187</v>
+        <v>1139</v>
       </c>
       <c r="D4">
-        <v>1067.97</v>
+        <v>1016.06</v>
       </c>
       <c r="E4">
-        <v>345.27</v>
+        <v>327.82</v>
       </c>
       <c r="F4">
-        <v>3107.39</v>
+        <v>2950.38</v>
       </c>
       <c r="G4">
         <v>11</v>
@@ -473,19 +473,19 @@
         </is>
       </c>
       <c r="B5">
-        <v>141489.21</v>
+        <v>146666.85</v>
       </c>
       <c r="C5">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="D5">
-        <v>206.68</v>
+        <v>211.68</v>
       </c>
       <c r="E5">
-        <v>118.81</v>
+        <v>115.53</v>
       </c>
       <c r="F5">
-        <v>2825.66</v>
+        <v>2904.45</v>
       </c>
       <c r="G5">
         <v>550</v>
@@ -498,19 +498,19 @@
         </is>
       </c>
       <c r="B6">
-        <v>18921.33</v>
+        <v>18142.03</v>
       </c>
       <c r="C6">
-        <v>610</v>
+        <v>585</v>
       </c>
       <c r="D6">
-        <v>458.17</v>
+        <v>412.43</v>
       </c>
       <c r="E6">
-        <v>274.17</v>
+        <v>277.82</v>
       </c>
       <c r="F6">
-        <v>1825.87</v>
+        <v>1680.83</v>
       </c>
       <c r="G6">
         <v>31</v>
@@ -523,19 +523,19 @@
         </is>
       </c>
       <c r="B7">
-        <v>28261.73</v>
+        <v>27617.94</v>
       </c>
       <c r="C7">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="D7">
-        <v>203.44</v>
+        <v>194.32</v>
       </c>
       <c r="E7">
-        <v>139.1</v>
+        <v>141.04</v>
       </c>
       <c r="F7">
-        <v>1454.05</v>
+        <v>1383.74</v>
       </c>
       <c r="G7">
         <v>90</v>
@@ -548,19 +548,19 @@
         </is>
       </c>
       <c r="B8">
-        <v>131914.73</v>
+        <v>127240.85</v>
       </c>
       <c r="C8">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="D8">
-        <v>296.17</v>
+        <v>286.25</v>
       </c>
       <c r="E8">
-        <v>184.64</v>
+        <v>178.71</v>
       </c>
       <c r="F8">
-        <v>2260</v>
+        <v>2179.61</v>
       </c>
       <c r="G8">
         <v>350</v>
@@ -573,19 +573,19 @@
         </is>
       </c>
       <c r="B9">
-        <v>81272.72</v>
+        <v>84006.77</v>
       </c>
       <c r="C9">
-        <v>475</v>
+        <v>491</v>
       </c>
       <c r="D9">
-        <v>427.06</v>
+        <v>445.58</v>
       </c>
       <c r="E9">
-        <v>199.08</v>
+        <v>208.03</v>
       </c>
       <c r="F9">
-        <v>3016.09</v>
+        <v>3144.34</v>
       </c>
       <c r="G9">
         <v>171</v>
@@ -598,19 +598,19 @@
         </is>
       </c>
       <c r="B10">
-        <v>9722892.630000001</v>
+        <v>9821128.92</v>
       </c>
       <c r="C10">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="D10">
-        <v>561.73</v>
+        <v>561.75</v>
       </c>
       <c r="E10">
-        <v>127.9</v>
+        <v>123.1</v>
       </c>
       <c r="F10">
-        <v>23067.77</v>
+        <v>22791.71</v>
       </c>
       <c r="G10">
         <v>16857</v>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="B11">
-        <v>421218.58</v>
+        <v>420160.22</v>
       </c>
       <c r="C11">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D11">
-        <v>789.34</v>
+        <v>787.1799999999999</v>
       </c>
       <c r="E11">
-        <v>158.08</v>
+        <v>157.39</v>
       </c>
       <c r="F11">
-        <v>25589.22</v>
+        <v>25525.41</v>
       </c>
       <c r="G11">
         <v>1197</v>
@@ -648,19 +648,19 @@
         </is>
       </c>
       <c r="B12">
-        <v>1641405.44</v>
+        <v>1780079.73</v>
       </c>
       <c r="C12">
-        <v>493</v>
+        <v>534</v>
       </c>
       <c r="D12">
-        <v>545.87</v>
+        <v>596.74</v>
       </c>
       <c r="E12">
-        <v>107.15</v>
+        <v>115.33</v>
       </c>
       <c r="F12">
-        <v>5333.53</v>
+        <v>5839.92</v>
       </c>
       <c r="G12">
         <v>3331</v>
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="B13">
-        <v>138655.75</v>
+        <v>149378.82</v>
       </c>
       <c r="C13">
-        <v>394</v>
+        <v>424</v>
       </c>
       <c r="D13">
-        <v>276.95</v>
+        <v>298.06</v>
       </c>
       <c r="E13">
-        <v>145.32</v>
+        <v>156.42</v>
       </c>
       <c r="F13">
-        <v>2523.07</v>
+        <v>2715.22</v>
       </c>
       <c r="G13">
         <v>352</v>
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="B14">
-        <v>92564.10000000001</v>
+        <v>101035.42</v>
       </c>
       <c r="C14">
-        <v>1076</v>
+        <v>1175</v>
       </c>
       <c r="D14">
-        <v>977.46</v>
+        <v>1083.35</v>
       </c>
       <c r="E14">
-        <v>251.3</v>
+        <v>278.66</v>
       </c>
       <c r="F14">
-        <v>4005.07</v>
+        <v>4394.56</v>
       </c>
       <c r="G14">
         <v>86</v>
@@ -723,19 +723,19 @@
         </is>
       </c>
       <c r="B15">
-        <v>721.27</v>
+        <v>794.51</v>
       </c>
       <c r="C15">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>240.42</v>
+        <v>264.84</v>
       </c>
       <c r="F15">
-        <v>240.42</v>
+        <v>264.84</v>
       </c>
       <c r="G15">
         <v>3</v>
@@ -748,19 +748,19 @@
         </is>
       </c>
       <c r="B16">
-        <v>100610.59</v>
+        <v>104759.37</v>
       </c>
       <c r="C16">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="D16">
-        <v>351.1</v>
+        <v>362.24</v>
       </c>
       <c r="E16">
-        <v>173.54</v>
+        <v>178.34</v>
       </c>
       <c r="F16">
-        <v>3114.65</v>
+        <v>3232.55</v>
       </c>
       <c r="G16">
         <v>258</v>
@@ -773,19 +773,19 @@
         </is>
       </c>
       <c r="B17">
-        <v>170076.38</v>
+        <v>157601.83</v>
       </c>
       <c r="C17">
-        <v>565</v>
+        <v>524</v>
       </c>
       <c r="D17">
-        <v>503.46</v>
+        <v>463.68</v>
       </c>
       <c r="E17">
-        <v>182.51</v>
+        <v>162.77</v>
       </c>
       <c r="F17">
-        <v>5272.15</v>
+        <v>4848.18</v>
       </c>
       <c r="G17">
         <v>301</v>
@@ -798,19 +798,19 @@
         </is>
       </c>
       <c r="B18">
-        <v>170726.84</v>
+        <v>176197.02</v>
       </c>
       <c r="C18">
-        <v>476</v>
+        <v>491</v>
       </c>
       <c r="D18">
-        <v>458.87</v>
+        <v>481.68</v>
       </c>
       <c r="E18">
-        <v>152.14</v>
+        <v>160.23</v>
       </c>
       <c r="F18">
-        <v>3070.06</v>
+        <v>3221.77</v>
       </c>
       <c r="G18">
         <v>359</v>
@@ -823,19 +823,19 @@
         </is>
       </c>
       <c r="B19">
-        <v>7854.52</v>
+        <v>7950.85</v>
       </c>
       <c r="C19">
-        <v>1309</v>
+        <v>1325</v>
       </c>
       <c r="D19">
-        <v>978.11</v>
+        <v>996.55</v>
       </c>
       <c r="E19">
-        <v>185.66</v>
+        <v>178.03</v>
       </c>
       <c r="F19">
-        <v>2482.86</v>
+        <v>2500.57</v>
       </c>
       <c r="G19">
         <v>6</v>
@@ -848,19 +848,19 @@
         </is>
       </c>
       <c r="B20">
-        <v>15166.9</v>
+        <v>18037.5</v>
       </c>
       <c r="C20">
-        <v>460</v>
+        <v>547</v>
       </c>
       <c r="D20">
-        <v>326.96</v>
+        <v>348.1</v>
       </c>
       <c r="E20">
-        <v>257.1</v>
+        <v>319.52</v>
       </c>
       <c r="F20">
-        <v>1496.24</v>
+        <v>1652.47</v>
       </c>
       <c r="G20">
         <v>33</v>
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="B21">
-        <v>19349.61</v>
+        <v>18453.55</v>
       </c>
       <c r="C21">
-        <v>553</v>
+        <v>527</v>
       </c>
       <c r="D21">
-        <v>328.31</v>
+        <v>318.4</v>
       </c>
       <c r="E21">
-        <v>281.12</v>
+        <v>255.7</v>
       </c>
       <c r="F21">
-        <v>1744.25</v>
+        <v>1717.86</v>
       </c>
       <c r="G21">
         <v>35</v>
@@ -898,19 +898,19 @@
         </is>
       </c>
       <c r="B22">
-        <v>10144.03</v>
+        <v>10307.25</v>
       </c>
       <c r="C22">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="D22">
-        <v>211.04</v>
+        <v>214.25</v>
       </c>
       <c r="E22">
-        <v>226.95</v>
+        <v>230.36</v>
       </c>
       <c r="F22">
-        <v>988.62</v>
+        <v>1004.14</v>
       </c>
       <c r="G22">
         <v>22</v>
@@ -923,19 +923,19 @@
         </is>
       </c>
       <c r="B23">
-        <v>36419.56</v>
+        <v>31099.27</v>
       </c>
       <c r="C23">
-        <v>12140</v>
+        <v>10366</v>
       </c>
       <c r="D23">
-        <v>10260.37</v>
+        <v>8763.309999999999</v>
       </c>
       <c r="E23">
-        <v>642.21</v>
+        <v>548.13</v>
       </c>
       <c r="F23">
-        <v>20364.24</v>
+        <v>17396.03</v>
       </c>
       <c r="G23">
         <v>3</v>
@@ -948,19 +948,19 @@
         </is>
       </c>
       <c r="B24">
-        <v>84414.28999999999</v>
+        <v>54196.73</v>
       </c>
       <c r="C24">
-        <v>314</v>
+        <v>201</v>
       </c>
       <c r="D24">
-        <v>341.67</v>
+        <v>162.27</v>
       </c>
       <c r="E24">
-        <v>84.93000000000001</v>
+        <v>136.09</v>
       </c>
       <c r="F24">
-        <v>3369.67</v>
+        <v>1599.29</v>
       </c>
       <c r="G24">
         <v>269</v>
@@ -973,19 +973,19 @@
         </is>
       </c>
       <c r="B25">
-        <v>73037.2</v>
+        <v>80076.60000000001</v>
       </c>
       <c r="C25">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="D25">
-        <v>94.55</v>
+        <v>105.46</v>
       </c>
       <c r="E25">
-        <v>91.03</v>
+        <v>89.19</v>
       </c>
       <c r="F25">
-        <v>781.85</v>
+        <v>862.84</v>
       </c>
       <c r="G25">
         <v>374</v>
@@ -998,19 +998,19 @@
         </is>
       </c>
       <c r="B26">
-        <v>302230.14</v>
+        <v>283870.66</v>
       </c>
       <c r="C26">
-        <v>628</v>
+        <v>590</v>
       </c>
       <c r="D26">
-        <v>566.46</v>
+        <v>527.86</v>
       </c>
       <c r="E26">
-        <v>179.75</v>
+        <v>179.65</v>
       </c>
       <c r="F26">
-        <v>3852.24</v>
+        <v>3588.63</v>
       </c>
       <c r="G26">
         <v>481</v>
@@ -1023,19 +1023,19 @@
         </is>
       </c>
       <c r="B27">
-        <v>3252.24</v>
+        <v>3307.88</v>
       </c>
       <c r="C27">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="D27">
-        <v>161.77</v>
+        <v>167.19</v>
       </c>
       <c r="E27">
-        <v>223.73</v>
+        <v>191.54</v>
       </c>
       <c r="F27">
-        <v>765.76</v>
+        <v>742.85</v>
       </c>
       <c r="G27">
         <v>10</v>
@@ -1048,19 +1048,19 @@
         </is>
       </c>
       <c r="B28">
-        <v>3414.43</v>
+        <v>3696.35</v>
       </c>
       <c r="C28">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="D28">
-        <v>115.49</v>
+        <v>124.18</v>
       </c>
       <c r="E28">
-        <v>185.94</v>
+        <v>201.64</v>
       </c>
       <c r="F28">
-        <v>591.5700000000001</v>
+        <v>638.35</v>
       </c>
       <c r="G28">
         <v>15</v>
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="B29">
-        <v>162.67</v>
+        <v>169.53</v>
       </c>
       <c r="C29">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="E29">
-        <v>162.67</v>
+        <v>169.53</v>
       </c>
       <c r="F29">
-        <v>162.67</v>
+        <v>169.53</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -1095,19 +1095,19 @@
         </is>
       </c>
       <c r="B30">
-        <v>2173.76</v>
+        <v>2380.26</v>
       </c>
       <c r="C30">
-        <v>311</v>
+        <v>340</v>
       </c>
       <c r="D30">
-        <v>290.48</v>
+        <v>318.08</v>
       </c>
       <c r="E30">
-        <v>135.86</v>
+        <v>148.77</v>
       </c>
       <c r="F30">
-        <v>951.02</v>
+        <v>1041.37</v>
       </c>
       <c r="G30">
         <v>7</v>
@@ -1120,19 +1120,19 @@
         </is>
       </c>
       <c r="B31">
-        <v>576749.09</v>
+        <v>561258.85</v>
       </c>
       <c r="C31">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="D31">
-        <v>1471.68</v>
+        <v>1437.38</v>
       </c>
       <c r="E31">
-        <v>98.83</v>
+        <v>98.73999999999999</v>
       </c>
       <c r="F31">
-        <v>27944.91</v>
+        <v>27206.36</v>
       </c>
       <c r="G31">
         <v>1141</v>
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="B32">
-        <v>361795.03</v>
+        <v>377300.7</v>
       </c>
       <c r="C32">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c r="D32">
-        <v>316.73</v>
+        <v>327.68</v>
       </c>
       <c r="E32">
-        <v>120.44</v>
+        <v>133.83</v>
       </c>
       <c r="F32">
-        <v>3696.02</v>
+        <v>3800.09</v>
       </c>
       <c r="G32">
         <v>957</v>
@@ -1170,19 +1170,19 @@
         </is>
       </c>
       <c r="B33">
-        <v>132919.49</v>
+        <v>141023.22</v>
       </c>
       <c r="C33">
-        <v>487</v>
+        <v>517</v>
       </c>
       <c r="D33">
-        <v>357.48</v>
+        <v>377.33</v>
       </c>
       <c r="E33">
-        <v>157.41</v>
+        <v>153.58</v>
       </c>
       <c r="F33">
-        <v>3036.7</v>
+        <v>3235.73</v>
       </c>
       <c r="G33">
         <v>273</v>
@@ -1195,19 +1195,19 @@
         </is>
       </c>
       <c r="B34">
-        <v>336330.37</v>
+        <v>349025.57</v>
       </c>
       <c r="C34">
-        <v>707</v>
+        <v>733</v>
       </c>
       <c r="D34">
-        <v>781.4</v>
+        <v>813.12</v>
       </c>
       <c r="E34">
-        <v>145.23</v>
+        <v>151.13</v>
       </c>
       <c r="F34">
-        <v>6685.31</v>
+        <v>6932.01</v>
       </c>
       <c r="G34">
         <v>476</v>
@@ -1220,19 +1220,19 @@
         </is>
       </c>
       <c r="B35">
-        <v>77683.95</v>
+        <v>63083.7</v>
       </c>
       <c r="C35">
-        <v>154</v>
+        <v>125</v>
       </c>
       <c r="D35">
-        <v>109.33</v>
+        <v>82.25</v>
       </c>
       <c r="E35">
-        <v>73.11</v>
+        <v>62.34</v>
       </c>
       <c r="F35">
-        <v>1067.97</v>
+        <v>699.04</v>
       </c>
       <c r="G35">
         <v>503</v>
@@ -1245,19 +1245,19 @@
         </is>
       </c>
       <c r="B36">
-        <v>6385.57</v>
+        <v>6396.94</v>
       </c>
       <c r="C36">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="D36">
-        <v>750.53</v>
+        <v>737.92</v>
       </c>
       <c r="E36">
-        <v>341.43</v>
+        <v>328.83</v>
       </c>
       <c r="F36">
-        <v>2390</v>
+        <v>2301.81</v>
       </c>
       <c r="G36">
         <v>7</v>
@@ -1270,19 +1270,19 @@
         </is>
       </c>
       <c r="B37">
-        <v>29148.14</v>
+        <v>27930.75</v>
       </c>
       <c r="C37">
-        <v>411</v>
+        <v>393</v>
       </c>
       <c r="D37">
-        <v>221.31</v>
+        <v>212.06</v>
       </c>
       <c r="E37">
-        <v>191.18</v>
+        <v>183.18</v>
       </c>
       <c r="F37">
-        <v>999.14</v>
+        <v>957.41</v>
       </c>
       <c r="G37">
         <v>71</v>
@@ -1295,19 +1295,19 @@
         </is>
       </c>
       <c r="B38">
-        <v>202669.6</v>
+        <v>214771</v>
       </c>
       <c r="C38">
-        <v>765</v>
+        <v>810</v>
       </c>
       <c r="D38">
-        <v>1131.26</v>
+        <v>1192.93</v>
       </c>
       <c r="E38">
-        <v>149.97</v>
+        <v>159.59</v>
       </c>
       <c r="F38">
-        <v>12051.09</v>
+        <v>12732.61</v>
       </c>
       <c r="G38">
         <v>265</v>
@@ -1320,16 +1320,16 @@
         </is>
       </c>
       <c r="B39">
-        <v>416.04</v>
+        <v>391.93</v>
       </c>
       <c r="C39">
-        <v>416</v>
+        <v>392</v>
       </c>
       <c r="E39">
-        <v>416.04</v>
+        <v>391.93</v>
       </c>
       <c r="F39">
-        <v>416.04</v>
+        <v>391.93</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -1342,19 +1342,19 @@
         </is>
       </c>
       <c r="B40">
-        <v>10575.95</v>
+        <v>7913.97</v>
       </c>
       <c r="C40">
-        <v>1511</v>
+        <v>1131</v>
       </c>
       <c r="D40">
-        <v>829.4299999999999</v>
+        <v>619.98</v>
       </c>
       <c r="E40">
-        <v>684.8</v>
+        <v>602.14</v>
       </c>
       <c r="F40">
-        <v>3094.35</v>
+        <v>2333.38</v>
       </c>
       <c r="G40">
         <v>7</v>
@@ -1367,19 +1367,19 @@
         </is>
       </c>
       <c r="B41">
-        <v>96034.89</v>
+        <v>117485.32</v>
       </c>
       <c r="C41">
-        <v>387</v>
+        <v>474</v>
       </c>
       <c r="D41">
-        <v>255.39</v>
+        <v>316.94</v>
       </c>
       <c r="E41">
-        <v>148.35</v>
+        <v>188.89</v>
       </c>
       <c r="F41">
-        <v>1393.02</v>
+        <v>1700.01</v>
       </c>
       <c r="G41">
         <v>248</v>
@@ -1392,19 +1392,19 @@
         </is>
       </c>
       <c r="B42">
-        <v>5589.19</v>
+        <v>5200.31</v>
       </c>
       <c r="C42">
-        <v>559</v>
+        <v>520</v>
       </c>
       <c r="D42">
-        <v>92.41</v>
+        <v>62.59</v>
       </c>
       <c r="E42">
-        <v>414.62</v>
+        <v>418.92</v>
       </c>
       <c r="F42">
-        <v>627.53</v>
+        <v>566.27</v>
       </c>
       <c r="G42">
         <v>10</v>
@@ -1417,19 +1417,19 @@
         </is>
       </c>
       <c r="B43">
-        <v>11422.09</v>
+        <v>13262.69</v>
       </c>
       <c r="C43">
-        <v>571</v>
+        <v>663</v>
       </c>
       <c r="D43">
-        <v>409.75</v>
+        <v>485.49</v>
       </c>
       <c r="E43">
-        <v>233.35</v>
+        <v>276.01</v>
       </c>
       <c r="F43">
-        <v>1633.44</v>
+        <v>1932.05</v>
       </c>
       <c r="G43">
         <v>20</v>
@@ -1442,19 +1442,19 @@
         </is>
       </c>
       <c r="B44">
-        <v>385763.82</v>
+        <v>429428.62</v>
       </c>
       <c r="C44">
-        <v>1217</v>
+        <v>1355</v>
       </c>
       <c r="D44">
-        <v>1617.34</v>
+        <v>1869.18</v>
       </c>
       <c r="E44">
-        <v>252.31</v>
+        <v>294.66</v>
       </c>
       <c r="F44">
-        <v>16700.46</v>
+        <v>19176.83</v>
       </c>
       <c r="G44">
         <v>317</v>
@@ -1467,19 +1467,19 @@
         </is>
       </c>
       <c r="B45">
-        <v>58976.79</v>
+        <v>58013.42</v>
       </c>
       <c r="C45">
-        <v>1787</v>
+        <v>1758</v>
       </c>
       <c r="D45">
-        <v>3401.92</v>
+        <v>3349.58</v>
       </c>
       <c r="E45">
-        <v>158.93</v>
+        <v>175.54</v>
       </c>
       <c r="F45">
-        <v>17688.28</v>
+        <v>17495.04</v>
       </c>
       <c r="G45">
         <v>33</v>
@@ -1492,19 +1492,19 @@
         </is>
       </c>
       <c r="B46">
-        <v>19516.53</v>
+        <v>13186.16</v>
       </c>
       <c r="C46">
-        <v>1501</v>
+        <v>1014</v>
       </c>
       <c r="D46">
-        <v>1050.97</v>
+        <v>696.17</v>
       </c>
       <c r="E46">
-        <v>677.53</v>
+        <v>463.35</v>
       </c>
       <c r="F46">
-        <v>3358</v>
+        <v>2236.77</v>
       </c>
       <c r="G46">
         <v>13</v>
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="B47">
-        <v>19434.54</v>
+        <v>19566.93</v>
       </c>
       <c r="C47">
-        <v>1296</v>
+        <v>1304</v>
       </c>
       <c r="D47">
-        <v>2824.82</v>
+        <v>2777.93</v>
       </c>
       <c r="E47">
-        <v>220.06</v>
+        <v>217</v>
       </c>
       <c r="F47">
-        <v>11443.2</v>
+        <v>11283.97</v>
       </c>
       <c r="G47">
         <v>15</v>
@@ -1542,19 +1542,19 @@
         </is>
       </c>
       <c r="B48">
-        <v>200246.1</v>
+        <v>208412.33</v>
       </c>
       <c r="C48">
-        <v>1472</v>
+        <v>1532</v>
       </c>
       <c r="D48">
-        <v>2455.77</v>
+        <v>2368.03</v>
       </c>
       <c r="E48">
-        <v>14.17</v>
+        <v>80.09</v>
       </c>
       <c r="F48">
-        <v>14687.27</v>
+        <v>13789.65</v>
       </c>
       <c r="G48">
         <v>136</v>
@@ -1567,19 +1567,19 @@
         </is>
       </c>
       <c r="B49">
-        <v>746843.14</v>
+        <v>771905.26</v>
       </c>
       <c r="C49">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="D49">
-        <v>342.56</v>
+        <v>356.04</v>
       </c>
       <c r="E49">
-        <v>131.32</v>
+        <v>135.62</v>
       </c>
       <c r="F49">
-        <v>4787.19</v>
+        <v>4998.58</v>
       </c>
       <c r="G49">
         <v>2020</v>
@@ -1592,19 +1592,19 @@
         </is>
       </c>
       <c r="B50">
-        <v>607.05</v>
+        <v>1111.02</v>
       </c>
       <c r="C50">
-        <v>87</v>
+        <v>159</v>
       </c>
       <c r="D50">
-        <v>47.62</v>
+        <v>89.94</v>
       </c>
       <c r="E50">
-        <v>27.41</v>
+        <v>28.91</v>
       </c>
       <c r="F50">
-        <v>165.47</v>
+        <v>292.21</v>
       </c>
       <c r="G50">
         <v>7</v>
@@ -1617,19 +1617,19 @@
         </is>
       </c>
       <c r="B51">
-        <v>11921.52</v>
+        <v>12129.68</v>
       </c>
       <c r="C51">
-        <v>1192</v>
+        <v>1213</v>
       </c>
       <c r="D51">
-        <v>920.05</v>
+        <v>930.5</v>
       </c>
       <c r="E51">
-        <v>288.81</v>
+        <v>246.97</v>
       </c>
       <c r="F51">
-        <v>3490.25</v>
+        <v>3529.53</v>
       </c>
       <c r="G51">
         <v>10</v>
@@ -1642,19 +1642,19 @@
         </is>
       </c>
       <c r="B52">
-        <v>207322.01</v>
+        <v>221316.03</v>
       </c>
       <c r="C52">
-        <v>693</v>
+        <v>740</v>
       </c>
       <c r="D52">
-        <v>819.6</v>
+        <v>876.48</v>
       </c>
       <c r="E52">
-        <v>62.61</v>
+        <v>65.73</v>
       </c>
       <c r="F52">
-        <v>3793.48</v>
+        <v>4149.34</v>
       </c>
       <c r="G52">
         <v>299</v>
@@ -1667,16 +1667,16 @@
         </is>
       </c>
       <c r="B53">
-        <v>763.46</v>
+        <v>590.53</v>
       </c>
       <c r="C53">
-        <v>763</v>
+        <v>591</v>
       </c>
       <c r="E53">
-        <v>763.46</v>
+        <v>590.53</v>
       </c>
       <c r="F53">
-        <v>763.46</v>
+        <v>590.53</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B54">
-        <v>11015.22</v>
+        <v>11632.03</v>
       </c>
       <c r="C54">
-        <v>1102</v>
+        <v>1163</v>
       </c>
       <c r="D54">
-        <v>766.0599999999999</v>
+        <v>893.73</v>
       </c>
       <c r="E54">
-        <v>214.85</v>
+        <v>120.52</v>
       </c>
       <c r="F54">
-        <v>2582.25</v>
+        <v>2821.45</v>
       </c>
       <c r="G54">
         <v>10</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B55">
-        <v>26739.29</v>
+        <v>23572.98</v>
       </c>
       <c r="C55">
-        <v>438</v>
+        <v>386</v>
       </c>
       <c r="D55">
-        <v>235.03</v>
+        <v>216.7</v>
       </c>
       <c r="E55">
-        <v>319.34</v>
+        <v>294.06</v>
       </c>
       <c r="F55">
-        <v>1916.04</v>
+        <v>1764.35</v>
       </c>
       <c r="G55">
         <v>61</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B56">
-        <v>46732.81</v>
+        <v>43366.65</v>
       </c>
       <c r="C56">
-        <v>399</v>
+        <v>371</v>
       </c>
       <c r="D56">
-        <v>171.31</v>
+        <v>132.67</v>
       </c>
       <c r="E56">
-        <v>326</v>
+        <v>248.29</v>
       </c>
       <c r="F56">
-        <v>1348.07</v>
+        <v>1065.57</v>
       </c>
       <c r="G56">
         <v>117</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B57">
-        <v>468752.74</v>
+        <v>490498.25</v>
       </c>
       <c r="C57">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="D57">
-        <v>675.3099999999999</v>
+        <v>706.35</v>
       </c>
       <c r="E57">
-        <v>101.54</v>
+        <v>102.92</v>
       </c>
       <c r="F57">
-        <v>11116.8</v>
+        <v>11627.57</v>
       </c>
       <c r="G57">
         <v>1116</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B58">
-        <v>1508.28</v>
+        <v>1280.43</v>
       </c>
       <c r="C58">
-        <v>754</v>
+        <v>640</v>
       </c>
       <c r="D58">
-        <v>718.23</v>
+        <v>606.41</v>
       </c>
       <c r="E58">
-        <v>246.27</v>
+        <v>211.42</v>
       </c>
       <c r="F58">
-        <v>1262.01</v>
+        <v>1069.01</v>
       </c>
       <c r="G58">
         <v>2</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B59">
-        <v>526352.52</v>
+        <v>538049.26</v>
       </c>
       <c r="C59">
-        <v>606</v>
+        <v>620</v>
       </c>
       <c r="D59">
-        <v>757.29</v>
+        <v>782.64</v>
       </c>
       <c r="E59">
-        <v>143.29</v>
+        <v>153.41</v>
       </c>
       <c r="F59">
-        <v>11000.48</v>
+        <v>11543.8</v>
       </c>
       <c r="G59">
         <v>868</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B60">
-        <v>35092.93</v>
+        <v>32064.89</v>
       </c>
       <c r="C60">
-        <v>285</v>
+        <v>261</v>
       </c>
       <c r="D60">
-        <v>240.31</v>
+        <v>214.22</v>
       </c>
       <c r="E60">
-        <v>158.63</v>
+        <v>138.05</v>
       </c>
       <c r="F60">
-        <v>1588.54</v>
+        <v>1400.11</v>
       </c>
       <c r="G60">
         <v>123</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B61">
-        <v>867.9</v>
+        <v>782.99</v>
       </c>
       <c r="C61">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="D61">
-        <v>68.52</v>
+        <v>90.47</v>
       </c>
       <c r="E61">
-        <v>65.34999999999999</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="F61">
-        <v>261.42</v>
+        <v>303.96</v>
       </c>
       <c r="G61">
         <v>6</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B62">
-        <v>900.9</v>
+        <v>1101.14</v>
       </c>
       <c r="C62">
-        <v>450</v>
+        <v>551</v>
       </c>
       <c r="D62">
-        <v>318.52</v>
+        <v>389.31</v>
       </c>
       <c r="E62">
-        <v>225.23</v>
+        <v>275.29</v>
       </c>
       <c r="F62">
-        <v>675.6799999999999</v>
+        <v>825.86</v>
       </c>
       <c r="G62">
         <v>2</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B63">
-        <v>735.95</v>
+        <v>804.02</v>
       </c>
       <c r="C63">
-        <v>368</v>
+        <v>402</v>
       </c>
       <c r="D63">
-        <v>184.41</v>
+        <v>206.61</v>
       </c>
       <c r="E63">
-        <v>237.58</v>
+        <v>255.91</v>
       </c>
       <c r="F63">
-        <v>498.37</v>
+        <v>548.11</v>
       </c>
       <c r="G63">
         <v>2</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B64">
-        <v>18255.02</v>
+        <v>17786.12</v>
       </c>
       <c r="C64">
-        <v>702</v>
+        <v>684</v>
       </c>
       <c r="D64">
-        <v>617.83</v>
+        <v>609.78</v>
       </c>
       <c r="E64">
-        <v>291.42</v>
+        <v>288.24</v>
       </c>
       <c r="F64">
-        <v>2331.35</v>
+        <v>2305.92</v>
       </c>
       <c r="G64">
         <v>26</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B65">
-        <v>828.66</v>
+        <v>1120.15</v>
       </c>
       <c r="C65">
-        <v>276</v>
+        <v>373</v>
       </c>
       <c r="D65">
-        <v>97.47</v>
+        <v>143.2</v>
       </c>
       <c r="E65">
-        <v>163.67</v>
+        <v>208.03</v>
       </c>
       <c r="F65">
-        <v>332.49</v>
+        <v>456.06</v>
       </c>
       <c r="G65">
         <v>3</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B66">
-        <v>3124.49</v>
+        <v>2120.42</v>
       </c>
       <c r="C66">
-        <v>625</v>
+        <v>424</v>
       </c>
       <c r="D66">
-        <v>452.62</v>
+        <v>327.37</v>
       </c>
       <c r="E66">
-        <v>161.82</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="F66">
-        <v>1337.19</v>
+        <v>926.16</v>
       </c>
       <c r="G66">
         <v>5</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B67">
-        <v>201065.68</v>
+        <v>219309.67</v>
       </c>
       <c r="C67">
-        <v>759</v>
+        <v>828</v>
       </c>
       <c r="D67">
-        <v>783.03</v>
+        <v>856.16</v>
       </c>
       <c r="E67">
-        <v>155.09</v>
+        <v>161.37</v>
       </c>
       <c r="F67">
-        <v>5194.85</v>
+        <v>5681.43</v>
       </c>
       <c r="G67">
         <v>265</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B68">
-        <v>80406.2</v>
+        <v>75369.83</v>
       </c>
       <c r="C68">
-        <v>1101</v>
+        <v>1032</v>
       </c>
       <c r="D68">
-        <v>1812.29</v>
+        <v>1827.37</v>
       </c>
       <c r="E68">
-        <v>155.3</v>
+        <v>153.46</v>
       </c>
       <c r="F68">
-        <v>9165.040000000001</v>
+        <v>9331.42</v>
       </c>
       <c r="G68">
         <v>73</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B69">
-        <v>5381.24</v>
+        <v>11206.76</v>
       </c>
       <c r="C69">
-        <v>186</v>
+        <v>386</v>
       </c>
       <c r="D69">
-        <v>147.24</v>
+        <v>342.95</v>
       </c>
       <c r="E69">
-        <v>99.05</v>
+        <v>60.17</v>
       </c>
       <c r="F69">
-        <v>795.66</v>
+        <v>1747.34</v>
       </c>
       <c r="G69">
         <v>29</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B70">
-        <v>437988.17</v>
+        <v>428837.51</v>
       </c>
       <c r="C70">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="D70">
-        <v>538.59</v>
+        <v>533.99</v>
       </c>
       <c r="E70">
-        <v>174.75</v>
+        <v>178</v>
       </c>
       <c r="F70">
-        <v>6104.8</v>
+        <v>6020.16</v>
       </c>
       <c r="G70">
         <v>765</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B71">
-        <v>96872.64999999999</v>
+        <v>100738.93</v>
       </c>
       <c r="C71">
-        <v>431</v>
+        <v>448</v>
       </c>
       <c r="D71">
-        <v>195.33</v>
+        <v>208.58</v>
       </c>
       <c r="E71">
-        <v>363.76</v>
+        <v>374.01</v>
       </c>
       <c r="F71">
-        <v>1818.81</v>
+        <v>1870.06</v>
       </c>
       <c r="G71">
         <v>225</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B72">
-        <v>1102701.74</v>
+        <v>1158629.99</v>
       </c>
       <c r="C72">
-        <v>503</v>
+        <v>528</v>
       </c>
       <c r="D72">
-        <v>513.78</v>
+        <v>535.97</v>
       </c>
       <c r="E72">
-        <v>123.45</v>
+        <v>129.85</v>
       </c>
       <c r="F72">
-        <v>10791.6</v>
+        <v>11251.2</v>
       </c>
       <c r="G72">
         <v>2193</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B73">
-        <v>703.04</v>
+        <v>708.53</v>
       </c>
       <c r="C73">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D73">
         <v>0</v>
       </c>
       <c r="E73">
-        <v>351.52</v>
+        <v>354.27</v>
       </c>
       <c r="F73">
-        <v>351.52</v>
+        <v>354.27</v>
       </c>
       <c r="G73">
         <v>2</v>
@@ -2189,19 +2189,19 @@
         </is>
       </c>
       <c r="B74">
-        <v>1289188.02</v>
+        <v>1277010.91</v>
       </c>
       <c r="C74">
-        <v>938</v>
+        <v>929</v>
       </c>
       <c r="D74">
-        <v>1475.97</v>
+        <v>1446.75</v>
       </c>
       <c r="E74">
-        <v>242.54</v>
+        <v>234.68</v>
       </c>
       <c r="F74">
-        <v>30749.62</v>
+        <v>30068.19</v>
       </c>
       <c r="G74">
         <v>1374</v>
@@ -2214,19 +2214,19 @@
         </is>
       </c>
       <c r="B75">
-        <v>19594.09</v>
+        <v>26546.11</v>
       </c>
       <c r="C75">
-        <v>332</v>
+        <v>450</v>
       </c>
       <c r="D75">
-        <v>324.46</v>
+        <v>418.05</v>
       </c>
       <c r="E75">
-        <v>139.23</v>
+        <v>196.58</v>
       </c>
       <c r="F75">
-        <v>1997.37</v>
+        <v>2555.57</v>
       </c>
       <c r="G75">
         <v>59</v>
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="B76">
-        <v>11534.43</v>
+        <v>11440.9</v>
       </c>
       <c r="C76">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D76">
-        <v>328.76</v>
+        <v>309.43</v>
       </c>
       <c r="E76">
-        <v>87.12</v>
+        <v>82.33</v>
       </c>
       <c r="F76">
-        <v>2526.51</v>
+        <v>2387.6</v>
       </c>
       <c r="G76">
         <v>58</v>
@@ -2264,19 +2264,19 @@
         </is>
       </c>
       <c r="B77">
-        <v>1168.62</v>
+        <v>1207.73</v>
       </c>
       <c r="C77">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="D77">
-        <v>92.53</v>
+        <v>98.13</v>
       </c>
       <c r="E77">
-        <v>186.25</v>
+        <v>189.08</v>
       </c>
       <c r="F77">
-        <v>398.06</v>
+        <v>414.78</v>
       </c>
       <c r="G77">
         <v>5</v>
@@ -2289,19 +2289,19 @@
         </is>
       </c>
       <c r="B78">
-        <v>404786.37</v>
+        <v>427041.46</v>
       </c>
       <c r="C78">
-        <v>448</v>
+        <v>472</v>
       </c>
       <c r="D78">
-        <v>341.02</v>
+        <v>359.3</v>
       </c>
       <c r="E78">
-        <v>153.42</v>
+        <v>159.7</v>
       </c>
       <c r="F78">
-        <v>4156.05</v>
+        <v>4378.05</v>
       </c>
       <c r="G78">
         <v>904</v>
@@ -2314,19 +2314,19 @@
         </is>
       </c>
       <c r="B79">
-        <v>41060.47</v>
+        <v>40640.82</v>
       </c>
       <c r="C79">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="D79">
-        <v>311.4</v>
+        <v>304.45</v>
       </c>
       <c r="E79">
-        <v>132.81</v>
+        <v>150.42</v>
       </c>
       <c r="F79">
-        <v>2639.73</v>
+        <v>2575.73</v>
       </c>
       <c r="G79">
         <v>117</v>
@@ -2339,19 +2339,19 @@
         </is>
       </c>
       <c r="B80">
-        <v>2718314.1</v>
+        <v>2922688.14</v>
       </c>
       <c r="C80">
-        <v>501</v>
+        <v>539</v>
       </c>
       <c r="D80">
-        <v>497.59</v>
+        <v>531.8099999999999</v>
       </c>
       <c r="E80">
-        <v>85.90000000000001</v>
+        <v>90.05</v>
       </c>
       <c r="F80">
-        <v>10629.28</v>
+        <v>11349.5</v>
       </c>
       <c r="G80">
         <v>5425</v>
@@ -2364,19 +2364,19 @@
         </is>
       </c>
       <c r="B81">
-        <v>372309.75</v>
+        <v>384202.89</v>
       </c>
       <c r="C81">
-        <v>600</v>
+        <v>619</v>
       </c>
       <c r="D81">
-        <v>875.35</v>
+        <v>910.45</v>
       </c>
       <c r="E81">
-        <v>124.18</v>
+        <v>131.74</v>
       </c>
       <c r="F81">
-        <v>10810.27</v>
+        <v>11244.61</v>
       </c>
       <c r="G81">
         <v>621</v>
@@ -2389,19 +2389,19 @@
         </is>
       </c>
       <c r="B82">
-        <v>50645.5</v>
+        <v>53331.43</v>
       </c>
       <c r="C82">
-        <v>576</v>
+        <v>606</v>
       </c>
       <c r="D82">
-        <v>609.1799999999999</v>
+        <v>603.85</v>
       </c>
       <c r="E82">
-        <v>225.93</v>
+        <v>225.82</v>
       </c>
       <c r="F82">
-        <v>4541.6</v>
+        <v>4583.92</v>
       </c>
       <c r="G82">
         <v>88</v>
@@ -2414,19 +2414,19 @@
         </is>
       </c>
       <c r="B83">
-        <v>154037.16</v>
+        <v>146677.13</v>
       </c>
       <c r="C83">
-        <v>414</v>
+        <v>394</v>
       </c>
       <c r="D83">
-        <v>451.35</v>
+        <v>423.82</v>
       </c>
       <c r="E83">
-        <v>99.95</v>
+        <v>93.91</v>
       </c>
       <c r="F83">
-        <v>3198.51</v>
+        <v>3005.01</v>
       </c>
       <c r="G83">
         <v>372</v>
@@ -2439,19 +2439,19 @@
         </is>
       </c>
       <c r="B84">
-        <v>83531.06</v>
+        <v>95600.86</v>
       </c>
       <c r="C84">
-        <v>370</v>
+        <v>423</v>
       </c>
       <c r="D84">
-        <v>428.89</v>
+        <v>481.75</v>
       </c>
       <c r="E84">
-        <v>115.55</v>
+        <v>126.62</v>
       </c>
       <c r="F84">
-        <v>4528.83</v>
+        <v>5017.69</v>
       </c>
       <c r="G84">
         <v>226</v>
@@ -2464,19 +2464,19 @@
         </is>
       </c>
       <c r="B85">
-        <v>33767.01</v>
+        <v>35563.02</v>
       </c>
       <c r="C85">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="D85">
-        <v>135.63</v>
+        <v>139.11</v>
       </c>
       <c r="E85">
-        <v>103.23</v>
+        <v>106.73</v>
       </c>
       <c r="F85">
-        <v>829.22</v>
+        <v>853.8099999999999</v>
       </c>
       <c r="G85">
         <v>178</v>
@@ -2489,19 +2489,19 @@
         </is>
       </c>
       <c r="B86">
-        <v>27753.16</v>
+        <v>32000.13</v>
       </c>
       <c r="C86">
-        <v>1461</v>
+        <v>1684</v>
       </c>
       <c r="D86">
-        <v>2090.64</v>
+        <v>2435.36</v>
       </c>
       <c r="E86">
-        <v>274.89</v>
+        <v>319.46</v>
       </c>
       <c r="F86">
-        <v>9587.780000000001</v>
+        <v>11151.77</v>
       </c>
       <c r="G86">
         <v>19</v>
@@ -2514,19 +2514,19 @@
         </is>
       </c>
       <c r="B87">
-        <v>902.99</v>
+        <v>744.99</v>
       </c>
       <c r="C87">
-        <v>226</v>
+        <v>186</v>
       </c>
       <c r="D87">
-        <v>93.34999999999999</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="E87">
-        <v>108.71</v>
+        <v>105.65</v>
       </c>
       <c r="F87">
-        <v>301</v>
+        <v>248.33</v>
       </c>
       <c r="G87">
         <v>4</v>
@@ -2539,19 +2539,19 @@
         </is>
       </c>
       <c r="B88">
-        <v>92645.85000000001</v>
+        <v>91158.05</v>
       </c>
       <c r="C88">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="D88">
-        <v>269.94</v>
+        <v>262.21</v>
       </c>
       <c r="E88">
-        <v>180.41</v>
+        <v>174.83</v>
       </c>
       <c r="F88">
-        <v>2164.88</v>
+        <v>2097.99</v>
       </c>
       <c r="G88">
         <v>255</v>
@@ -2564,19 +2564,19 @@
         </is>
       </c>
       <c r="B89">
-        <v>7474.89</v>
+        <v>7928.1</v>
       </c>
       <c r="C89">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="D89">
-        <v>123.92</v>
+        <v>133.07</v>
       </c>
       <c r="E89">
-        <v>118.66</v>
+        <v>123.76</v>
       </c>
       <c r="F89">
-        <v>551.53</v>
+        <v>589.51</v>
       </c>
       <c r="G89">
         <v>40</v>
@@ -2589,19 +2589,19 @@
         </is>
       </c>
       <c r="B90">
-        <v>7807.44</v>
+        <v>7125</v>
       </c>
       <c r="C90">
-        <v>520</v>
+        <v>475</v>
       </c>
       <c r="D90">
-        <v>417.54</v>
+        <v>383</v>
       </c>
       <c r="E90">
-        <v>175</v>
+        <v>160.99</v>
       </c>
       <c r="F90">
-        <v>1601.87</v>
+        <v>1459.27</v>
       </c>
       <c r="G90">
         <v>15</v>
@@ -2639,19 +2639,19 @@
         </is>
       </c>
       <c r="B92">
-        <v>645336.65</v>
+        <v>464415.12</v>
       </c>
       <c r="C92">
-        <v>3309</v>
+        <v>2382</v>
       </c>
       <c r="D92">
-        <v>7329.27</v>
+        <v>5301.87</v>
       </c>
       <c r="E92">
-        <v>574.48</v>
+        <v>421.37</v>
       </c>
       <c r="F92">
-        <v>74829.34</v>
+        <v>53520.09</v>
       </c>
       <c r="G92">
         <v>195</v>
@@ -2664,16 +2664,16 @@
         </is>
       </c>
       <c r="B93">
-        <v>1491.71</v>
+        <v>1109.23</v>
       </c>
       <c r="C93">
-        <v>1492</v>
+        <v>1109</v>
       </c>
       <c r="E93">
-        <v>1491.71</v>
+        <v>1109.23</v>
       </c>
       <c r="F93">
-        <v>1491.71</v>
+        <v>1109.23</v>
       </c>
       <c r="G93">
         <v>1</v>
@@ -2686,19 +2686,19 @@
         </is>
       </c>
       <c r="B94">
-        <v>3225.32</v>
+        <v>7804.9</v>
       </c>
       <c r="C94">
-        <v>1075</v>
+        <v>2602</v>
       </c>
       <c r="D94">
-        <v>966.6900000000001</v>
+        <v>1384.1</v>
       </c>
       <c r="E94">
-        <v>516.99</v>
+        <v>1802.52</v>
       </c>
       <c r="F94">
-        <v>2191.34</v>
+        <v>4199.86</v>
       </c>
       <c r="G94">
         <v>3</v>
@@ -2711,19 +2711,19 @@
         </is>
       </c>
       <c r="B95">
-        <v>383078.88</v>
+        <v>483091.66</v>
       </c>
       <c r="C95">
-        <v>810</v>
+        <v>1021</v>
       </c>
       <c r="D95">
-        <v>1399.51</v>
+        <v>1786.48</v>
       </c>
       <c r="E95">
-        <v>179.37</v>
+        <v>281.6</v>
       </c>
       <c r="F95">
-        <v>19039.8</v>
+        <v>22347.9</v>
       </c>
       <c r="G95">
         <v>473</v>
@@ -2736,19 +2736,19 @@
         </is>
       </c>
       <c r="B96">
-        <v>27245.52</v>
+        <v>30939.02</v>
       </c>
       <c r="C96">
-        <v>851</v>
+        <v>967</v>
       </c>
       <c r="D96">
-        <v>918.61</v>
+        <v>1144.8</v>
       </c>
       <c r="E96">
-        <v>256.47</v>
+        <v>251.86</v>
       </c>
       <c r="F96">
-        <v>3751.51</v>
+        <v>5110.94</v>
       </c>
       <c r="G96">
         <v>32</v>
@@ -2761,19 +2761,19 @@
         </is>
       </c>
       <c r="B97">
-        <v>107927.74</v>
+        <v>94096.02</v>
       </c>
       <c r="C97">
-        <v>818</v>
+        <v>713</v>
       </c>
       <c r="D97">
-        <v>1074.06</v>
+        <v>1013.88</v>
       </c>
       <c r="E97">
-        <v>111.78</v>
+        <v>117.94</v>
       </c>
       <c r="F97">
-        <v>7067.05</v>
+        <v>6343.78</v>
       </c>
       <c r="G97">
         <v>132</v>
@@ -2786,19 +2786,19 @@
         </is>
       </c>
       <c r="B98">
-        <v>22982.98</v>
+        <v>23642.26</v>
       </c>
       <c r="C98">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D98">
-        <v>46.6</v>
+        <v>48.74</v>
       </c>
       <c r="E98">
-        <v>119.81</v>
+        <v>122.66</v>
       </c>
       <c r="F98">
-        <v>479.24</v>
+        <v>490.64</v>
       </c>
       <c r="G98">
         <v>171</v>
@@ -2811,19 +2811,19 @@
         </is>
       </c>
       <c r="B99">
-        <v>249190.29</v>
+        <v>357804.75</v>
       </c>
       <c r="C99">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="D99">
-        <v>92.92</v>
+        <v>134.05</v>
       </c>
       <c r="E99">
-        <v>31.46</v>
+        <v>44.74</v>
       </c>
       <c r="F99">
-        <v>2293.9</v>
+        <v>3311.7</v>
       </c>
       <c r="G99">
         <v>2973</v>
@@ -2836,19 +2836,19 @@
         </is>
       </c>
       <c r="B100">
-        <v>10654.16</v>
+        <v>14996.69</v>
       </c>
       <c r="C100">
-        <v>304</v>
+        <v>428</v>
       </c>
       <c r="D100">
-        <v>240.77</v>
+        <v>335.86</v>
       </c>
       <c r="E100">
-        <v>70.5</v>
+        <v>103.54</v>
       </c>
       <c r="F100">
-        <v>886.42</v>
+        <v>1239.47</v>
       </c>
       <c r="G100">
         <v>35</v>
@@ -2861,19 +2861,19 @@
         </is>
       </c>
       <c r="B101">
-        <v>224379.06</v>
+        <v>232185.13</v>
       </c>
       <c r="C101">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="D101">
-        <v>207.58</v>
+        <v>214.74</v>
       </c>
       <c r="E101">
-        <v>107.53</v>
+        <v>111.62</v>
       </c>
       <c r="F101">
-        <v>2401.56</v>
+        <v>2494.14</v>
       </c>
       <c r="G101">
         <v>786</v>

--- a/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Output_costs_by_tretspef-Users_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Output_costs_by_tretspef-Users_Raw.xlsx
@@ -401,19 +401,19 @@
         <v>349011.9</v>
       </c>
       <c r="C2">
-        <v>329</v>
+        <v>287</v>
       </c>
       <c r="D2">
-        <v>313.84</v>
+        <v>251.99</v>
       </c>
       <c r="E2">
         <v>135.31</v>
       </c>
       <c r="F2">
-        <v>4777.91</v>
+        <v>4256.88</v>
       </c>
       <c r="G2">
-        <v>1062</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="3">
@@ -426,19 +426,19 @@
         <v>400851.58</v>
       </c>
       <c r="C3">
-        <v>384</v>
+        <v>320</v>
       </c>
       <c r="D3">
-        <v>384.37</v>
+        <v>287.62</v>
       </c>
       <c r="E3">
         <v>118.14</v>
       </c>
       <c r="F3">
-        <v>5855.61</v>
+        <v>6519.05</v>
       </c>
       <c r="G3">
-        <v>1043</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="4">
@@ -451,19 +451,19 @@
         <v>12523.94</v>
       </c>
       <c r="C4">
-        <v>1139</v>
+        <v>737</v>
       </c>
       <c r="D4">
-        <v>1016.06</v>
+        <v>546.59</v>
       </c>
       <c r="E4">
         <v>327.82</v>
       </c>
       <c r="F4">
-        <v>2950.38</v>
+        <v>2018.18</v>
       </c>
       <c r="G4">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -476,19 +476,19 @@
         <v>146666.85</v>
       </c>
       <c r="C5">
-        <v>267</v>
+        <v>238</v>
       </c>
       <c r="D5">
-        <v>211.68</v>
+        <v>142.22</v>
       </c>
       <c r="E5">
         <v>115.53</v>
       </c>
       <c r="F5">
-        <v>2904.45</v>
+        <v>1859.53</v>
       </c>
       <c r="G5">
-        <v>550</v>
+        <v>615</v>
       </c>
     </row>
     <row r="6">
@@ -501,19 +501,19 @@
         <v>18142.03</v>
       </c>
       <c r="C6">
-        <v>585</v>
+        <v>477</v>
       </c>
       <c r="D6">
-        <v>412.43</v>
+        <v>283.22</v>
       </c>
       <c r="E6">
         <v>277.82</v>
       </c>
       <c r="F6">
-        <v>1680.83</v>
+        <v>1125.19</v>
       </c>
       <c r="G6">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
@@ -526,19 +526,19 @@
         <v>27617.94</v>
       </c>
       <c r="C7">
-        <v>307</v>
+        <v>258</v>
       </c>
       <c r="D7">
-        <v>194.32</v>
+        <v>126.34</v>
       </c>
       <c r="E7">
         <v>141.04</v>
       </c>
       <c r="F7">
-        <v>1383.74</v>
+        <v>864.84</v>
       </c>
       <c r="G7">
-        <v>90</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8">
@@ -551,19 +551,19 @@
         <v>127240.85</v>
       </c>
       <c r="C8">
-        <v>364</v>
+        <v>303</v>
       </c>
       <c r="D8">
-        <v>286.25</v>
+        <v>200.26</v>
       </c>
       <c r="E8">
         <v>178.71</v>
       </c>
       <c r="F8">
-        <v>2179.61</v>
+        <v>1429.71</v>
       </c>
       <c r="G8">
-        <v>350</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9">
@@ -576,19 +576,19 @@
         <v>84006.77</v>
       </c>
       <c r="C9">
-        <v>491</v>
+        <v>394</v>
       </c>
       <c r="D9">
-        <v>445.58</v>
+        <v>316.17</v>
       </c>
       <c r="E9">
         <v>208.03</v>
       </c>
       <c r="F9">
-        <v>3144.34</v>
+        <v>2936.3</v>
       </c>
       <c r="G9">
-        <v>171</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
-        <v>9821128.92</v>
+        <v>9540012.970000001</v>
       </c>
       <c r="C10">
-        <v>583</v>
+        <v>679</v>
       </c>
       <c r="D10">
-        <v>561.75</v>
+        <v>768.08</v>
       </c>
       <c r="E10">
         <v>123.1</v>
       </c>
       <c r="F10">
-        <v>22791.71</v>
+        <v>16758.23</v>
       </c>
       <c r="G10">
-        <v>16857</v>
+        <v>14049</v>
       </c>
     </row>
     <row r="11">
@@ -626,19 +626,19 @@
         <v>420160.22</v>
       </c>
       <c r="C11">
-        <v>351</v>
+        <v>287</v>
       </c>
       <c r="D11">
-        <v>787.1799999999999</v>
+        <v>246.25</v>
       </c>
       <c r="E11">
-        <v>157.39</v>
+        <v>122.09</v>
       </c>
       <c r="F11">
-        <v>25525.41</v>
+        <v>4197.79</v>
       </c>
       <c r="G11">
-        <v>1197</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="12">
@@ -651,19 +651,19 @@
         <v>1780079.73</v>
       </c>
       <c r="C12">
-        <v>534</v>
+        <v>398</v>
       </c>
       <c r="D12">
-        <v>596.74</v>
+        <v>399.64</v>
       </c>
       <c r="E12">
         <v>115.33</v>
       </c>
       <c r="F12">
-        <v>5839.92</v>
+        <v>7168.81</v>
       </c>
       <c r="G12">
-        <v>3331</v>
+        <v>4469</v>
       </c>
     </row>
     <row r="13">
@@ -676,19 +676,19 @@
         <v>149378.82</v>
       </c>
       <c r="C13">
-        <v>424</v>
+        <v>351</v>
       </c>
       <c r="D13">
-        <v>298.06</v>
+        <v>228.54</v>
       </c>
       <c r="E13">
         <v>156.42</v>
       </c>
       <c r="F13">
-        <v>2715.22</v>
+        <v>1684.16</v>
       </c>
       <c r="G13">
-        <v>352</v>
+        <v>425</v>
       </c>
     </row>
     <row r="14">
@@ -701,19 +701,19 @@
         <v>101035.42</v>
       </c>
       <c r="C14">
-        <v>1175</v>
+        <v>722</v>
       </c>
       <c r="D14">
-        <v>1083.35</v>
+        <v>600.51</v>
       </c>
       <c r="E14">
         <v>278.66</v>
       </c>
       <c r="F14">
-        <v>4394.56</v>
+        <v>3172.59</v>
       </c>
       <c r="G14">
-        <v>86</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15">
@@ -751,19 +751,19 @@
         <v>104759.37</v>
       </c>
       <c r="C16">
-        <v>406</v>
+        <v>330</v>
       </c>
       <c r="D16">
-        <v>362.24</v>
+        <v>229.19</v>
       </c>
       <c r="E16">
         <v>178.34</v>
       </c>
       <c r="F16">
-        <v>3232.55</v>
+        <v>2001.86</v>
       </c>
       <c r="G16">
-        <v>258</v>
+        <v>317</v>
       </c>
     </row>
     <row r="17">
@@ -776,19 +776,19 @@
         <v>157601.83</v>
       </c>
       <c r="C17">
-        <v>524</v>
+        <v>396</v>
       </c>
       <c r="D17">
-        <v>463.68</v>
+        <v>292.77</v>
       </c>
       <c r="E17">
         <v>162.77</v>
       </c>
       <c r="F17">
-        <v>4848.18</v>
+        <v>3305.58</v>
       </c>
       <c r="G17">
-        <v>301</v>
+        <v>398</v>
       </c>
     </row>
     <row r="18">
@@ -801,19 +801,19 @@
         <v>176197.02</v>
       </c>
       <c r="C18">
-        <v>491</v>
+        <v>328</v>
       </c>
       <c r="D18">
-        <v>481.68</v>
+        <v>249.82</v>
       </c>
       <c r="E18">
         <v>160.23</v>
       </c>
       <c r="F18">
-        <v>3221.77</v>
+        <v>1779.74</v>
       </c>
       <c r="G18">
-        <v>359</v>
+        <v>538</v>
       </c>
     </row>
     <row r="19">
@@ -826,19 +826,19 @@
         <v>7950.85</v>
       </c>
       <c r="C19">
-        <v>1325</v>
+        <v>883</v>
       </c>
       <c r="D19">
-        <v>996.55</v>
+        <v>813.55</v>
       </c>
       <c r="E19">
-        <v>178.03</v>
+        <v>163.87</v>
       </c>
       <c r="F19">
-        <v>2500.57</v>
+        <v>2336.7</v>
       </c>
       <c r="G19">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -851,19 +851,19 @@
         <v>18037.5</v>
       </c>
       <c r="C20">
-        <v>547</v>
+        <v>429</v>
       </c>
       <c r="D20">
-        <v>348.1</v>
+        <v>194.42</v>
       </c>
       <c r="E20">
         <v>319.52</v>
       </c>
       <c r="F20">
-        <v>1652.47</v>
+        <v>1228.94</v>
       </c>
       <c r="G20">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21">
@@ -876,19 +876,19 @@
         <v>18453.55</v>
       </c>
       <c r="C21">
-        <v>527</v>
+        <v>401</v>
       </c>
       <c r="D21">
-        <v>318.4</v>
+        <v>177.47</v>
       </c>
       <c r="E21">
         <v>255.7</v>
       </c>
       <c r="F21">
-        <v>1717.86</v>
+        <v>986.78</v>
       </c>
       <c r="G21">
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22">
@@ -901,10 +901,10 @@
         <v>10307.25</v>
       </c>
       <c r="C22">
-        <v>469</v>
+        <v>382</v>
       </c>
       <c r="D22">
-        <v>214.25</v>
+        <v>180.66</v>
       </c>
       <c r="E22">
         <v>230.36</v>
@@ -913,7 +913,7 @@
         <v>1004.14</v>
       </c>
       <c r="G22">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23">
@@ -926,19 +926,19 @@
         <v>31099.27</v>
       </c>
       <c r="C23">
-        <v>10366</v>
+        <v>2827</v>
       </c>
       <c r="D23">
-        <v>8763.309999999999</v>
+        <v>2354.64</v>
       </c>
       <c r="E23">
         <v>548.13</v>
       </c>
       <c r="F23">
-        <v>17396.03</v>
+        <v>8077.83</v>
       </c>
       <c r="G23">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -951,19 +951,19 @@
         <v>54196.73</v>
       </c>
       <c r="C24">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="D24">
-        <v>162.27</v>
+        <v>128.22</v>
       </c>
       <c r="E24">
         <v>136.09</v>
       </c>
       <c r="F24">
-        <v>1599.29</v>
+        <v>1508.35</v>
       </c>
       <c r="G24">
-        <v>269</v>
+        <v>291</v>
       </c>
     </row>
     <row r="25">
@@ -976,19 +976,19 @@
         <v>80076.60000000001</v>
       </c>
       <c r="C25">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D25">
-        <v>105.46</v>
+        <v>89.08</v>
       </c>
       <c r="E25">
         <v>89.19</v>
       </c>
       <c r="F25">
-        <v>862.84</v>
+        <v>773.96</v>
       </c>
       <c r="G25">
-        <v>374</v>
+        <v>403</v>
       </c>
     </row>
     <row r="26">
@@ -1001,19 +1001,19 @@
         <v>283870.66</v>
       </c>
       <c r="C26">
-        <v>590</v>
+        <v>426</v>
       </c>
       <c r="D26">
-        <v>527.86</v>
+        <v>348.37</v>
       </c>
       <c r="E26">
         <v>179.65</v>
       </c>
       <c r="F26">
-        <v>3588.63</v>
+        <v>3157.31</v>
       </c>
       <c r="G26">
-        <v>481</v>
+        <v>666</v>
       </c>
     </row>
     <row r="27">
@@ -1026,19 +1026,19 @@
         <v>3307.88</v>
       </c>
       <c r="C27">
-        <v>331</v>
+        <v>301</v>
       </c>
       <c r="D27">
-        <v>167.19</v>
+        <v>86.83</v>
       </c>
       <c r="E27">
         <v>191.54</v>
       </c>
       <c r="F27">
-        <v>742.85</v>
+        <v>383.07</v>
       </c>
       <c r="G27">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28">
@@ -1098,19 +1098,19 @@
         <v>2380.26</v>
       </c>
       <c r="C30">
-        <v>340</v>
+        <v>216</v>
       </c>
       <c r="D30">
-        <v>318.08</v>
+        <v>154.08</v>
       </c>
       <c r="E30">
         <v>148.77</v>
       </c>
       <c r="F30">
-        <v>1041.37</v>
+        <v>595.0700000000001</v>
       </c>
       <c r="G30">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31">
@@ -1120,22 +1120,22 @@
         </is>
       </c>
       <c r="B31">
-        <v>561258.85</v>
+        <v>745208.04</v>
       </c>
       <c r="C31">
-        <v>492</v>
+        <v>424</v>
       </c>
       <c r="D31">
-        <v>1437.38</v>
+        <v>493.17</v>
       </c>
       <c r="E31">
         <v>98.73999999999999</v>
       </c>
       <c r="F31">
-        <v>27206.36</v>
+        <v>5368.73</v>
       </c>
       <c r="G31">
-        <v>1141</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="32">
@@ -1148,19 +1148,19 @@
         <v>377300.7</v>
       </c>
       <c r="C32">
-        <v>394</v>
+        <v>323</v>
       </c>
       <c r="D32">
-        <v>327.68</v>
+        <v>221.8</v>
       </c>
       <c r="E32">
         <v>133.83</v>
       </c>
       <c r="F32">
-        <v>3800.09</v>
+        <v>2136.2</v>
       </c>
       <c r="G32">
-        <v>957</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="33">
@@ -1173,19 +1173,19 @@
         <v>141023.22</v>
       </c>
       <c r="C33">
-        <v>517</v>
+        <v>394</v>
       </c>
       <c r="D33">
-        <v>377.33</v>
+        <v>256.09</v>
       </c>
       <c r="E33">
         <v>153.58</v>
       </c>
       <c r="F33">
-        <v>3235.73</v>
+        <v>2306.41</v>
       </c>
       <c r="G33">
-        <v>273</v>
+        <v>358</v>
       </c>
     </row>
     <row r="34">
@@ -1198,19 +1198,19 @@
         <v>349025.57</v>
       </c>
       <c r="C34">
-        <v>733</v>
+        <v>462</v>
       </c>
       <c r="D34">
-        <v>813.12</v>
+        <v>403.71</v>
       </c>
       <c r="E34">
         <v>151.13</v>
       </c>
       <c r="F34">
-        <v>6932.01</v>
+        <v>4726.96</v>
       </c>
       <c r="G34">
-        <v>476</v>
+        <v>755</v>
       </c>
     </row>
     <row r="35">
@@ -1223,19 +1223,19 @@
         <v>63083.7</v>
       </c>
       <c r="C35">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="D35">
-        <v>82.25</v>
+        <v>64.58</v>
       </c>
       <c r="E35">
         <v>62.34</v>
       </c>
       <c r="F35">
-        <v>699.04</v>
+        <v>548.9400000000001</v>
       </c>
       <c r="G35">
-        <v>503</v>
+        <v>543</v>
       </c>
     </row>
     <row r="36">
@@ -1248,19 +1248,19 @@
         <v>6396.94</v>
       </c>
       <c r="C36">
-        <v>914</v>
+        <v>582</v>
       </c>
       <c r="D36">
-        <v>737.92</v>
+        <v>344.36</v>
       </c>
       <c r="E36">
         <v>328.83</v>
       </c>
       <c r="F36">
-        <v>2301.81</v>
+        <v>1315.32</v>
       </c>
       <c r="G36">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37">
@@ -1273,19 +1273,19 @@
         <v>27930.75</v>
       </c>
       <c r="C37">
-        <v>393</v>
+        <v>317</v>
       </c>
       <c r="D37">
-        <v>212.06</v>
+        <v>170.58</v>
       </c>
       <c r="E37">
         <v>183.18</v>
       </c>
       <c r="F37">
-        <v>957.41</v>
+        <v>774.22</v>
       </c>
       <c r="G37">
-        <v>71</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38">
@@ -1298,19 +1298,19 @@
         <v>214771</v>
       </c>
       <c r="C38">
-        <v>810</v>
+        <v>519</v>
       </c>
       <c r="D38">
-        <v>1192.93</v>
+        <v>525.95</v>
       </c>
       <c r="E38">
         <v>159.59</v>
       </c>
       <c r="F38">
-        <v>12732.61</v>
+        <v>4694.67</v>
       </c>
       <c r="G38">
-        <v>265</v>
+        <v>414</v>
       </c>
     </row>
     <row r="39">
@@ -1345,19 +1345,19 @@
         <v>7913.97</v>
       </c>
       <c r="C40">
-        <v>1131</v>
+        <v>989</v>
       </c>
       <c r="D40">
-        <v>619.98</v>
+        <v>680.6900000000001</v>
       </c>
       <c r="E40">
-        <v>602.14</v>
+        <v>301.07</v>
       </c>
       <c r="F40">
         <v>2333.38</v>
       </c>
       <c r="G40">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
@@ -1370,19 +1370,19 @@
         <v>117485.32</v>
       </c>
       <c r="C41">
-        <v>474</v>
+        <v>366</v>
       </c>
       <c r="D41">
-        <v>316.94</v>
+        <v>220.99</v>
       </c>
       <c r="E41">
-        <v>188.89</v>
+        <v>134.67</v>
       </c>
       <c r="F41">
-        <v>1700.01</v>
+        <v>1267.02</v>
       </c>
       <c r="G41">
-        <v>248</v>
+        <v>321</v>
       </c>
     </row>
     <row r="42">
@@ -1420,19 +1420,19 @@
         <v>13262.69</v>
       </c>
       <c r="C43">
-        <v>663</v>
+        <v>428</v>
       </c>
       <c r="D43">
-        <v>485.49</v>
+        <v>218.13</v>
       </c>
       <c r="E43">
         <v>276.01</v>
       </c>
       <c r="F43">
-        <v>1932.05</v>
+        <v>967.8200000000001</v>
       </c>
       <c r="G43">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44">
@@ -1445,19 +1445,19 @@
         <v>429428.62</v>
       </c>
       <c r="C44">
-        <v>1355</v>
+        <v>850</v>
       </c>
       <c r="D44">
-        <v>1869.18</v>
+        <v>1049.74</v>
       </c>
       <c r="E44">
-        <v>294.66</v>
+        <v>214.09</v>
       </c>
       <c r="F44">
-        <v>19176.83</v>
+        <v>13578.28</v>
       </c>
       <c r="G44">
-        <v>317</v>
+        <v>505</v>
       </c>
     </row>
     <row r="45">
@@ -1470,19 +1470,19 @@
         <v>58013.42</v>
       </c>
       <c r="C45">
-        <v>1758</v>
+        <v>879</v>
       </c>
       <c r="D45">
-        <v>3349.58</v>
+        <v>803.67</v>
       </c>
       <c r="E45">
         <v>175.54</v>
       </c>
       <c r="F45">
-        <v>17495.04</v>
+        <v>3715.5</v>
       </c>
       <c r="G45">
-        <v>33</v>
+        <v>66</v>
       </c>
     </row>
     <row r="46">
@@ -1495,19 +1495,19 @@
         <v>13186.16</v>
       </c>
       <c r="C46">
-        <v>1014</v>
+        <v>733</v>
       </c>
       <c r="D46">
-        <v>696.17</v>
+        <v>563.35</v>
       </c>
       <c r="E46">
-        <v>463.35</v>
+        <v>319.54</v>
       </c>
       <c r="F46">
         <v>2236.77</v>
       </c>
       <c r="G46">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47">
@@ -1520,19 +1520,19 @@
         <v>19566.93</v>
       </c>
       <c r="C47">
-        <v>1304</v>
+        <v>652</v>
       </c>
       <c r="D47">
-        <v>2777.93</v>
+        <v>729.24</v>
       </c>
       <c r="E47">
         <v>217</v>
       </c>
       <c r="F47">
-        <v>11283.97</v>
+        <v>3254.99</v>
       </c>
       <c r="G47">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48">
@@ -1542,22 +1542,22 @@
         </is>
       </c>
       <c r="B48">
-        <v>208412.33</v>
+        <v>255273.43</v>
       </c>
       <c r="C48">
-        <v>1532</v>
+        <v>493</v>
       </c>
       <c r="D48">
-        <v>2368.03</v>
+        <v>551.13</v>
       </c>
       <c r="E48">
         <v>80.09</v>
       </c>
       <c r="F48">
-        <v>13789.65</v>
+        <v>4371.81</v>
       </c>
       <c r="G48">
-        <v>136</v>
+        <v>518</v>
       </c>
     </row>
     <row r="49">
@@ -1570,19 +1570,19 @@
         <v>771905.26</v>
       </c>
       <c r="C49">
-        <v>382</v>
+        <v>312</v>
       </c>
       <c r="D49">
-        <v>356.04</v>
+        <v>238.01</v>
       </c>
       <c r="E49">
         <v>135.62</v>
       </c>
       <c r="F49">
-        <v>4998.58</v>
+        <v>2404.21</v>
       </c>
       <c r="G49">
-        <v>2020</v>
+        <v>2473</v>
       </c>
     </row>
     <row r="50">
@@ -1620,19 +1620,19 @@
         <v>12129.68</v>
       </c>
       <c r="C51">
-        <v>1213</v>
+        <v>758</v>
       </c>
       <c r="D51">
-        <v>930.5</v>
+        <v>343.1</v>
       </c>
       <c r="E51">
         <v>246.97</v>
       </c>
       <c r="F51">
-        <v>3529.53</v>
+        <v>1411.81</v>
       </c>
       <c r="G51">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52">
@@ -1645,19 +1645,19 @@
         <v>221316.03</v>
       </c>
       <c r="C52">
-        <v>740</v>
+        <v>282</v>
       </c>
       <c r="D52">
-        <v>876.48</v>
+        <v>299.33</v>
       </c>
       <c r="E52">
         <v>65.73</v>
       </c>
       <c r="F52">
-        <v>4149.34</v>
+        <v>2679.7</v>
       </c>
       <c r="G52">
-        <v>299</v>
+        <v>784</v>
       </c>
     </row>
     <row r="53">
@@ -1692,19 +1692,19 @@
         <v>11632.03</v>
       </c>
       <c r="C54">
-        <v>1163</v>
+        <v>554</v>
       </c>
       <c r="D54">
-        <v>893.73</v>
+        <v>674.79</v>
       </c>
       <c r="E54">
-        <v>120.52</v>
+        <v>112.19</v>
       </c>
       <c r="F54">
         <v>2821.45</v>
       </c>
       <c r="G54">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55">
@@ -1717,10 +1717,10 @@
         <v>23572.98</v>
       </c>
       <c r="C55">
-        <v>386</v>
+        <v>363</v>
       </c>
       <c r="D55">
-        <v>216.7</v>
+        <v>204.41</v>
       </c>
       <c r="E55">
         <v>294.06</v>
@@ -1729,7 +1729,7 @@
         <v>1764.35</v>
       </c>
       <c r="G55">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="56">
@@ -1742,19 +1742,19 @@
         <v>43366.65</v>
       </c>
       <c r="C56">
-        <v>371</v>
+        <v>344</v>
       </c>
       <c r="D56">
-        <v>132.67</v>
+        <v>97.2</v>
       </c>
       <c r="E56">
         <v>248.29</v>
       </c>
       <c r="F56">
-        <v>1065.57</v>
+        <v>817.28</v>
       </c>
       <c r="G56">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="57">
@@ -1767,19 +1767,19 @@
         <v>490498.25</v>
       </c>
       <c r="C57">
-        <v>440</v>
+        <v>342</v>
       </c>
       <c r="D57">
-        <v>706.35</v>
+        <v>316.01</v>
       </c>
       <c r="E57">
         <v>102.92</v>
       </c>
       <c r="F57">
-        <v>11627.57</v>
+        <v>3534.92</v>
       </c>
       <c r="G57">
-        <v>1116</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="58">
@@ -1792,19 +1792,19 @@
         <v>1280.43</v>
       </c>
       <c r="C58">
-        <v>640</v>
+        <v>427</v>
       </c>
       <c r="D58">
-        <v>606.41</v>
+        <v>373.06</v>
       </c>
       <c r="E58">
         <v>211.42</v>
       </c>
       <c r="F58">
-        <v>1069.01</v>
+        <v>857.59</v>
       </c>
       <c r="G58">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -1817,19 +1817,19 @@
         <v>538049.26</v>
       </c>
       <c r="C59">
-        <v>620</v>
+        <v>444</v>
       </c>
       <c r="D59">
-        <v>782.64</v>
+        <v>445.08</v>
       </c>
       <c r="E59">
         <v>153.41</v>
       </c>
       <c r="F59">
-        <v>11543.8</v>
+        <v>6855.61</v>
       </c>
       <c r="G59">
-        <v>868</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="60">
@@ -1842,19 +1842,19 @@
         <v>32064.89</v>
       </c>
       <c r="C60">
-        <v>261</v>
+        <v>217</v>
       </c>
       <c r="D60">
-        <v>214.22</v>
+        <v>156.91</v>
       </c>
       <c r="E60">
         <v>138.05</v>
       </c>
       <c r="F60">
-        <v>1400.11</v>
+        <v>1163.14</v>
       </c>
       <c r="G60">
-        <v>123</v>
+        <v>148</v>
       </c>
     </row>
     <row r="61">
@@ -1917,19 +1917,19 @@
         <v>804.02</v>
       </c>
       <c r="C63">
-        <v>402</v>
+        <v>268</v>
       </c>
       <c r="D63">
-        <v>206.61</v>
+        <v>128.38</v>
       </c>
       <c r="E63">
-        <v>255.91</v>
+        <v>146.1</v>
       </c>
       <c r="F63">
-        <v>548.11</v>
+        <v>402.01</v>
       </c>
       <c r="G63">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -1942,19 +1942,19 @@
         <v>17786.12</v>
       </c>
       <c r="C64">
-        <v>684</v>
+        <v>508</v>
       </c>
       <c r="D64">
-        <v>609.78</v>
+        <v>373.12</v>
       </c>
       <c r="E64">
         <v>288.24</v>
       </c>
       <c r="F64">
-        <v>2305.92</v>
+        <v>2088.89</v>
       </c>
       <c r="G64">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="65">
@@ -1992,19 +1992,19 @@
         <v>2120.42</v>
       </c>
       <c r="C66">
-        <v>424</v>
+        <v>353</v>
       </c>
       <c r="D66">
-        <v>327.37</v>
+        <v>205.92</v>
       </c>
       <c r="E66">
         <v>66.56999999999999</v>
       </c>
       <c r="F66">
-        <v>926.16</v>
+        <v>639.63</v>
       </c>
       <c r="G66">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67">
@@ -2017,19 +2017,19 @@
         <v>219309.67</v>
       </c>
       <c r="C67">
-        <v>828</v>
+        <v>503</v>
       </c>
       <c r="D67">
-        <v>856.16</v>
+        <v>466.25</v>
       </c>
       <c r="E67">
         <v>161.37</v>
       </c>
       <c r="F67">
-        <v>5681.43</v>
+        <v>3203.97</v>
       </c>
       <c r="G67">
-        <v>265</v>
+        <v>436</v>
       </c>
     </row>
     <row r="68">
@@ -2042,19 +2042,19 @@
         <v>75369.83</v>
       </c>
       <c r="C68">
-        <v>1032</v>
+        <v>580</v>
       </c>
       <c r="D68">
-        <v>1827.37</v>
+        <v>654.9299999999999</v>
       </c>
       <c r="E68">
         <v>153.46</v>
       </c>
       <c r="F68">
-        <v>9331.42</v>
+        <v>3808.74</v>
       </c>
       <c r="G68">
-        <v>73</v>
+        <v>130</v>
       </c>
     </row>
     <row r="69">
@@ -2067,19 +2067,19 @@
         <v>11206.76</v>
       </c>
       <c r="C69">
-        <v>386</v>
+        <v>340</v>
       </c>
       <c r="D69">
-        <v>342.95</v>
+        <v>241.41</v>
       </c>
       <c r="E69">
         <v>60.17</v>
       </c>
       <c r="F69">
-        <v>1747.34</v>
+        <v>964.1</v>
       </c>
       <c r="G69">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="70">
@@ -2092,19 +2092,19 @@
         <v>428837.51</v>
       </c>
       <c r="C70">
-        <v>561</v>
+        <v>433</v>
       </c>
       <c r="D70">
-        <v>533.99</v>
+        <v>334.95</v>
       </c>
       <c r="E70">
         <v>178</v>
       </c>
       <c r="F70">
-        <v>6020.16</v>
+        <v>3800.09</v>
       </c>
       <c r="G70">
-        <v>765</v>
+        <v>991</v>
       </c>
     </row>
     <row r="71">
@@ -2117,19 +2117,19 @@
         <v>100738.93</v>
       </c>
       <c r="C71">
-        <v>448</v>
+        <v>431</v>
       </c>
       <c r="D71">
-        <v>208.58</v>
+        <v>154.28</v>
       </c>
       <c r="E71">
         <v>374.01</v>
       </c>
       <c r="F71">
-        <v>1870.06</v>
+        <v>1490.01</v>
       </c>
       <c r="G71">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="72">
@@ -2142,19 +2142,19 @@
         <v>1158629.99</v>
       </c>
       <c r="C72">
-        <v>528</v>
+        <v>438</v>
       </c>
       <c r="D72">
-        <v>535.97</v>
+        <v>353.93</v>
       </c>
       <c r="E72">
         <v>129.85</v>
       </c>
       <c r="F72">
-        <v>11251.2</v>
+        <v>3564.42</v>
       </c>
       <c r="G72">
-        <v>2193</v>
+        <v>2647</v>
       </c>
     </row>
     <row r="73">
@@ -2192,19 +2192,19 @@
         <v>1277010.91</v>
       </c>
       <c r="C74">
-        <v>929</v>
+        <v>761</v>
       </c>
       <c r="D74">
-        <v>1446.75</v>
+        <v>687.71</v>
       </c>
       <c r="E74">
         <v>234.68</v>
       </c>
       <c r="F74">
-        <v>30068.19</v>
+        <v>10236.63</v>
       </c>
       <c r="G74">
-        <v>1374</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="75">
@@ -2217,19 +2217,19 @@
         <v>26546.11</v>
       </c>
       <c r="C75">
-        <v>450</v>
+        <v>320</v>
       </c>
       <c r="D75">
-        <v>418.05</v>
+        <v>239.08</v>
       </c>
       <c r="E75">
         <v>196.58</v>
       </c>
       <c r="F75">
-        <v>2555.57</v>
+        <v>1572.66</v>
       </c>
       <c r="G75">
-        <v>59</v>
+        <v>83</v>
       </c>
     </row>
     <row r="76">
@@ -2242,19 +2242,19 @@
         <v>11440.9</v>
       </c>
       <c r="C76">
-        <v>197</v>
+        <v>153</v>
       </c>
       <c r="D76">
-        <v>309.43</v>
+        <v>243.01</v>
       </c>
       <c r="E76">
         <v>82.33</v>
       </c>
       <c r="F76">
-        <v>2387.6</v>
+        <v>2140.61</v>
       </c>
       <c r="G76">
-        <v>58</v>
+        <v>75</v>
       </c>
     </row>
     <row r="77">
@@ -2292,19 +2292,19 @@
         <v>427041.46</v>
       </c>
       <c r="C78">
-        <v>472</v>
+        <v>373</v>
       </c>
       <c r="D78">
-        <v>359.3</v>
+        <v>248.8</v>
       </c>
       <c r="E78">
         <v>159.7</v>
       </c>
       <c r="F78">
-        <v>4378.05</v>
+        <v>2253.76</v>
       </c>
       <c r="G78">
-        <v>904</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="79">
@@ -2317,19 +2317,19 @@
         <v>40640.82</v>
       </c>
       <c r="C79">
-        <v>347</v>
+        <v>288</v>
       </c>
       <c r="D79">
-        <v>304.45</v>
+        <v>225.43</v>
       </c>
       <c r="E79">
         <v>150.42</v>
       </c>
       <c r="F79">
-        <v>2575.73</v>
+        <v>2175.49</v>
       </c>
       <c r="G79">
-        <v>117</v>
+        <v>141</v>
       </c>
     </row>
     <row r="80">
@@ -2342,19 +2342,19 @@
         <v>2922688.14</v>
       </c>
       <c r="C80">
-        <v>539</v>
+        <v>368</v>
       </c>
       <c r="D80">
-        <v>531.8099999999999</v>
+        <v>366.73</v>
       </c>
       <c r="E80">
         <v>90.05</v>
       </c>
       <c r="F80">
-        <v>11349.5</v>
+        <v>6585.97</v>
       </c>
       <c r="G80">
-        <v>5425</v>
+        <v>7937</v>
       </c>
     </row>
     <row r="81">
@@ -2367,19 +2367,19 @@
         <v>384202.89</v>
       </c>
       <c r="C81">
-        <v>619</v>
+        <v>369</v>
       </c>
       <c r="D81">
-        <v>910.45</v>
+        <v>425.75</v>
       </c>
       <c r="E81">
         <v>131.74</v>
       </c>
       <c r="F81">
-        <v>11244.61</v>
+        <v>6350.35</v>
       </c>
       <c r="G81">
-        <v>621</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="82">
@@ -2392,19 +2392,19 @@
         <v>53331.43</v>
       </c>
       <c r="C82">
-        <v>606</v>
+        <v>417</v>
       </c>
       <c r="D82">
-        <v>603.85</v>
+        <v>278.58</v>
       </c>
       <c r="E82">
         <v>225.82</v>
       </c>
       <c r="F82">
-        <v>4583.92</v>
+        <v>2258.17</v>
       </c>
       <c r="G82">
-        <v>88</v>
+        <v>128</v>
       </c>
     </row>
     <row r="83">
@@ -2417,19 +2417,19 @@
         <v>146677.13</v>
       </c>
       <c r="C83">
-        <v>394</v>
+        <v>231</v>
       </c>
       <c r="D83">
-        <v>423.82</v>
+        <v>212.51</v>
       </c>
       <c r="E83">
         <v>93.91</v>
       </c>
       <c r="F83">
-        <v>3005.01</v>
+        <v>2065.95</v>
       </c>
       <c r="G83">
-        <v>372</v>
+        <v>636</v>
       </c>
     </row>
     <row r="84">
@@ -2442,19 +2442,19 @@
         <v>95600.86</v>
       </c>
       <c r="C84">
-        <v>423</v>
+        <v>308</v>
       </c>
       <c r="D84">
-        <v>481.75</v>
+        <v>269.71</v>
       </c>
       <c r="E84">
         <v>126.62</v>
       </c>
       <c r="F84">
-        <v>5017.69</v>
+        <v>2428.13</v>
       </c>
       <c r="G84">
-        <v>226</v>
+        <v>310</v>
       </c>
     </row>
     <row r="85">
@@ -2467,19 +2467,19 @@
         <v>35563.02</v>
       </c>
       <c r="C85">
-        <v>200</v>
+        <v>159</v>
       </c>
       <c r="D85">
-        <v>139.11</v>
+        <v>103.67</v>
       </c>
       <c r="E85">
         <v>106.73</v>
       </c>
       <c r="F85">
-        <v>853.8099999999999</v>
+        <v>747.09</v>
       </c>
       <c r="G85">
-        <v>178</v>
+        <v>223</v>
       </c>
     </row>
     <row r="86">
@@ -2492,19 +2492,19 @@
         <v>32000.13</v>
       </c>
       <c r="C86">
-        <v>1684</v>
+        <v>842</v>
       </c>
       <c r="D86">
-        <v>2435.36</v>
+        <v>783.64</v>
       </c>
       <c r="E86">
-        <v>319.46</v>
+        <v>312.16</v>
       </c>
       <c r="F86">
-        <v>11151.77</v>
+        <v>3194.56</v>
       </c>
       <c r="G86">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="87">
@@ -2542,19 +2542,19 @@
         <v>91158.05</v>
       </c>
       <c r="C88">
-        <v>357</v>
+        <v>295</v>
       </c>
       <c r="D88">
-        <v>262.21</v>
+        <v>193.45</v>
       </c>
       <c r="E88">
         <v>174.83</v>
       </c>
       <c r="F88">
-        <v>2097.99</v>
+        <v>1748.32</v>
       </c>
       <c r="G88">
-        <v>255</v>
+        <v>309</v>
       </c>
     </row>
     <row r="89">
@@ -2567,10 +2567,10 @@
         <v>7928.1</v>
       </c>
       <c r="C89">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="D89">
-        <v>133.07</v>
+        <v>115.42</v>
       </c>
       <c r="E89">
         <v>123.76</v>
@@ -2579,7 +2579,7 @@
         <v>589.51</v>
       </c>
       <c r="G89">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="90">
@@ -2592,19 +2592,19 @@
         <v>7125</v>
       </c>
       <c r="C90">
-        <v>475</v>
+        <v>324</v>
       </c>
       <c r="D90">
-        <v>383</v>
+        <v>185.51</v>
       </c>
       <c r="E90">
         <v>160.99</v>
       </c>
       <c r="F90">
-        <v>1459.27</v>
+        <v>804.9400000000001</v>
       </c>
       <c r="G90">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="91">
@@ -2614,22 +2614,22 @@
         </is>
       </c>
       <c r="B91">
-        <v>785.58</v>
+        <v>2305.23</v>
       </c>
       <c r="C91">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D91">
-        <v>45.99</v>
+        <v>32.87</v>
       </c>
       <c r="E91">
         <v>12.88</v>
       </c>
       <c r="F91">
-        <v>206.05</v>
+        <v>141.66</v>
       </c>
       <c r="G91">
-        <v>41</v>
+        <v>98</v>
       </c>
     </row>
     <row r="92">
@@ -2642,19 +2642,19 @@
         <v>464415.12</v>
       </c>
       <c r="C92">
-        <v>2382</v>
+        <v>1433</v>
       </c>
       <c r="D92">
-        <v>5301.87</v>
+        <v>1497.33</v>
       </c>
       <c r="E92">
         <v>421.37</v>
       </c>
       <c r="F92">
-        <v>53520.09</v>
+        <v>9104.690000000001</v>
       </c>
       <c r="G92">
-        <v>195</v>
+        <v>324</v>
       </c>
     </row>
     <row r="93">
@@ -2714,19 +2714,19 @@
         <v>483091.66</v>
       </c>
       <c r="C95">
-        <v>1021</v>
+        <v>757</v>
       </c>
       <c r="D95">
-        <v>1786.48</v>
+        <v>853.3099999999999</v>
       </c>
       <c r="E95">
         <v>281.6</v>
       </c>
       <c r="F95">
-        <v>22347.9</v>
+        <v>7962.02</v>
       </c>
       <c r="G95">
-        <v>473</v>
+        <v>638</v>
       </c>
     </row>
     <row r="96">
@@ -2739,19 +2739,19 @@
         <v>30939.02</v>
       </c>
       <c r="C96">
-        <v>967</v>
+        <v>658</v>
       </c>
       <c r="D96">
-        <v>1144.8</v>
+        <v>708.54</v>
       </c>
       <c r="E96">
         <v>251.86</v>
       </c>
       <c r="F96">
-        <v>5110.94</v>
+        <v>3959.13</v>
       </c>
       <c r="G96">
-        <v>32</v>
+        <v>47</v>
       </c>
     </row>
     <row r="97">
@@ -2764,19 +2764,19 @@
         <v>94096.02</v>
       </c>
       <c r="C97">
-        <v>713</v>
+        <v>434</v>
       </c>
       <c r="D97">
-        <v>1013.88</v>
+        <v>473.39</v>
       </c>
       <c r="E97">
         <v>117.94</v>
       </c>
       <c r="F97">
-        <v>6343.78</v>
+        <v>3077.62</v>
       </c>
       <c r="G97">
-        <v>132</v>
+        <v>217</v>
       </c>
     </row>
     <row r="98">
@@ -2789,10 +2789,10 @@
         <v>23642.26</v>
       </c>
       <c r="C98">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="D98">
-        <v>48.74</v>
+        <v>55.06</v>
       </c>
       <c r="E98">
         <v>122.66</v>
@@ -2801,7 +2801,7 @@
         <v>490.64</v>
       </c>
       <c r="G98">
-        <v>171</v>
+        <v>161</v>
       </c>
     </row>
     <row r="99">
@@ -2811,22 +2811,22 @@
         </is>
       </c>
       <c r="B99">
-        <v>357804.75</v>
+        <v>363218.35</v>
       </c>
       <c r="C99">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D99">
-        <v>134.05</v>
+        <v>119.73</v>
       </c>
       <c r="E99">
         <v>44.74</v>
       </c>
       <c r="F99">
-        <v>3311.7</v>
+        <v>3104.21</v>
       </c>
       <c r="G99">
-        <v>2973</v>
+        <v>3166</v>
       </c>
     </row>
     <row r="100">
@@ -2839,19 +2839,19 @@
         <v>14996.69</v>
       </c>
       <c r="C100">
-        <v>428</v>
+        <v>300</v>
       </c>
       <c r="D100">
-        <v>335.86</v>
+        <v>220.68</v>
       </c>
       <c r="E100">
         <v>103.54</v>
       </c>
       <c r="F100">
-        <v>1239.47</v>
+        <v>885.34</v>
       </c>
       <c r="G100">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="101">
@@ -2864,19 +2864,19 @@
         <v>232185.13</v>
       </c>
       <c r="C101">
-        <v>295</v>
+        <v>234</v>
       </c>
       <c r="D101">
-        <v>214.74</v>
+        <v>162.68</v>
       </c>
       <c r="E101">
         <v>111.62</v>
       </c>
       <c r="F101">
-        <v>2494.14</v>
+        <v>1399.47</v>
       </c>
       <c r="G101">
-        <v>786</v>
+        <v>991</v>
       </c>
     </row>
   </sheetData>
